--- a/master_inventory.xlsx
+++ b/master_inventory.xlsx
@@ -427,7 +427,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>deposit_state</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1276,7 +1276,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://archive.icpsr.umich.edu/view/studies/38586/versions/V2</t>
+          <t>https://www.icpsr.umich.edu/sites/view/studies/38586/versions/V2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2042,90 +2042,70 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>110663</t>
+          <t>120088</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>superseded</t>
+          <t>current</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Land Cover by Census Tract, United States, 2001-2016</t>
+          <t>Code for merging ZCTA level datasets with the UDS Mapper ZIP code to ZCTA crosswalk</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>V1.0</t>
+          <t>V2.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9/11/2019</t>
+          <t>3/10/2021</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>10.3886/E110663V10</t>
+          <t>10.3886/E120088V21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10.3886/E110663</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>10.3886/ICPSR38598.v2</t>
-        </is>
-      </c>
+          <t>10.3886/E120088</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.openicpsr.org/openicpsr/project/110663</t>
+          <t>https://archive.icpsr.umich.edu/view/studies/120088</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Philippa Clarke; Robert Melendez</t>
+          <t>Megan Chenoweth; Anam Khan</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>land_cover</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>landcover_tract_2001-2016</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Census Tract</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2001-2016</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>tract_fips</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Census Tract</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+          <t>crosswalks</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>NO_O_UNIT_IN_FOLDER+NO_DICT</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>120088</t>
+          <t>127681</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2135,56 +2115,76 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Code for merging ZCTA level datasets with the UDS Mapper ZIP code to ZCTA crosswalk</t>
+          <t>Education and Training Services by Census Tract, United States, 2003-2017</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>V2.1</t>
+          <t>V1.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3/10/2021</t>
+          <t>12/7/2020</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10.3886/E120088V21</t>
+          <t>10.3886/E127681V14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10.3886/E120088</t>
+          <t>10.3886/E127681</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://archive.icpsr.umich.edu/view/studies/120088</t>
+          <t>https://www.openicpsr.org/openicpsr/project/127681/view</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Megan Chenoweth; Anam Khan</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>NO_O_FILES</t>
-        </is>
-      </c>
+          <t>Jessica Finlay; Mao Li; Michael Esposito; Iris Gomez-Lopez; Anam Khan; Philippa Clarke; Megan Chenoweth</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>education_training</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>edtrain_tract_2003-2017</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Census Tract (2010)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2003-2017</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>tract_fips10; year</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Census Tract</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>127681</t>
+          <t>127682</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Education and Training Services by Census Tract, United States, 2003-2017</t>
+          <t>Education and Training Services by ZIP Code Tabulation Area, United States, 2003-2017</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2209,18 +2209,18 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10.3886/E127681V14</t>
+          <t>10.3886/E127682V14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10.3886/E127681</t>
+          <t>10.3886/E127682</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.openicpsr.org/openicpsr/project/127681/view</t>
+          <t>https://www.openicpsr.org/openicpsr/project/127682/view</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2235,12 +2235,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>edtrain_tract_2003-2017</t>
+          <t>edtrain_zcta_2003-2017</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
+          <t>ZCTA (2019)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>tract_fips10; year</t>
+          <t>zcta19; year</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Census Tract</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
@@ -2263,7 +2263,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>127682</t>
+          <t>141121</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2273,76 +2273,56 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Education and Training Services by ZIP Code Tabulation Area, United States, 2003-2017</t>
+          <t>Historic Redlining Indicator for 2000, 2010, and 2020 US Census Tracts</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>V1.4</t>
+          <t>V3.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>12/7/2020</t>
+          <t>9/25/2023</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10.3886/E127682V14</t>
+          <t>10.3886/E141121V36</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10.3886/E127682</t>
+          <t>10.3886/E141121</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.openicpsr.org/openicpsr/project/127682/view</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/141121</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Jessica Finlay; Mao Li; Michael Esposito; Iris Gomez-Lopez; Anam Khan; Philippa Clarke; Megan Chenoweth</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>education_training</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>edtrain_zcta_2003-2017</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>ZCTA (2019)</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2003-2017</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>zcta19; year</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>ZCTA</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+          <t>Helen C.S. Meier; Bruce C. Mitchell</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>NO_O_FILES</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>141121</t>
+          <t>190141</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2352,38 +2332,38 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Historic Redlining Indicator for 2000, 2010, and 2020 US Census Tracts</t>
+          <t>Special Data Release for Neighborhood Context and Alzheimer's Disease and Related Dementias</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>V3.6</t>
+          <t>V1.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9/25/2023</t>
+          <t>5/11/2023</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>10.3886/E141121V36</t>
+          <t>10.3886/E190141V11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10.3886/E141121</t>
+          <t>10.3886/E190141</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/141121</t>
+          <t>https://www.openicpsr.org/openicpsr/project/190141/view</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Helen C.S. Meier; Bruce C. Mitchell</t>
+          <t>Robert Melendez; Philippa Clarke; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -2401,7 +2381,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>190141</t>
+          <t>200038</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2411,56 +2391,76 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Special Data Release for Neighborhood Context and Alzheimer's Disease and Related Dementias</t>
+          <t>Libraries by Census Tract and ZIP Code Tabulation Area, United States, 1992-2021</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>V1.1</t>
+          <t>V5.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5/11/2023</t>
+          <t>11/5/2025</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>10.3886/E190141V11</t>
+          <t>10.3886/ICPSR200038.V5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10.3886/E190141</t>
+          <t>10.3886/ICPSR200038.V5</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.openicpsr.org/openicpsr/project/190141/view</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/200038/versions/V5.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Robert Melendez; Philippa Clarke; Lindsay Gypin</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>NO_O_FILES</t>
-        </is>
-      </c>
+          <t>Robert Melendez; Philippa Clarke; William Milton Clary II; Grace Noppert; Lindsay Gypin</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>libraries</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>libraries_1992-2020</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1992-2020</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Census Tract</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>200038</t>
+          <t>207966</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2470,63 +2470,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Libraries by Census Tract and ZIP Code Tabulation Area, United States, 1992-2021</t>
+          <t>Civic, Social, and Religious Organizations by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>V5.0</t>
+          <t>V2.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11/5/2025</t>
+          <t>4/7/2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10.3886/ICPSR200038.V5</t>
+          <t>10.3886/E207966V22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10.3886/ICPSR200038.V5</t>
+          <t>10.3886/E207966</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/200038/versions/V5.0</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/207966</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Robert Melendez; Philippa Clarke; William Milton Clary II; Grace Noppert; Lindsay Gypin</t>
+          <t>Robert Melendez; William Milton Clary II; Philippa J. Clarke; Grace A. Noppert; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>libraries</t>
+          <t>religious_civic_social_orgs</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>libraries_1992-2020</t>
+          <t>relcivsoc_1990-2022</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
+          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1992-2020</t>
+          <t>1990-2022</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>207966</t>
+          <t>208207</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2549,33 +2549,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Civic, Social, and Religious Organizations by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Social Services by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>V2.2</t>
+          <t>V5.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4/7/2026</t>
+          <t>4/8/2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10.3886/E207966V22</t>
+          <t>10.3886/E208207V51</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>10.3886/E207966</t>
+          <t>10.3886/E208207</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/207966</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208207</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>religious_civic_social_orgs</t>
+          <t>social_services</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>relcivsoc_1990-2022</t>
+          <t>social_services_1990-2022</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2618,7 +2618,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>208207</t>
+          <t>208366</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2628,63 +2628,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Social Services by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Post Offices and Banks by Census Tract and ZCTA, United States, 1990-2021</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>V5.1</t>
+          <t>V2.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4/8/2026</t>
+          <t>2/11/2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10.3886/E208207V51</t>
+          <t>10.3886/E208366V22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>10.3886/E208207</t>
+          <t>10.3886/E208366</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208207</t>
+          <t>https://www.openicpsr.org/openicpsr/project/208366/view</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Robert Melendez; William Milton Clary II; Philippa J. Clarke; Grace A. Noppert; Lindsay Gypin</t>
+          <t>Robert Melendez; Jessica Finlay; Philippa Clarke; Grace Noppert; Lindsay Gypin; Ellis Dyke</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>social_services</t>
+          <t>post_offices_banks</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>social_services_1990-2022</t>
+          <t>pobank_1990-2021</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
+          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1990-2022</t>
+          <t>1990-2021</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
+          <t>tract_fips10; year; tract_fips20; zcta20; zcta10</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2697,7 +2697,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>208366</t>
+          <t>208682</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2707,63 +2707,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Post Offices and Banks by Census Tract and ZCTA, United States, 1990-2021</t>
+          <t>Retail Establishments by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>V2.2</t>
+          <t>V2.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2/11/2026</t>
+          <t>4/9/2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10.3886/E208366V22</t>
+          <t>10.3886/E208682V20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>10.3886/E208366</t>
+          <t>10.3886/E208682</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.openicpsr.org/openicpsr/project/208366/view</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208682</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Robert Melendez; Jessica Finlay; Philippa Clarke; Grace Noppert; Lindsay Gypin; Ellis Dyke</t>
+          <t>Robert Melendez; Philippa J. Clarke; Grace A. Noppert; Lindsay Gypin; William Milton Clary II</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>post_offices_banks</t>
+          <t>retail_establishments</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>pobank_1990-2021</t>
+          <t>retail_1990-2022</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
+          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1990-2021</t>
+          <t>1990-2022</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; zcta20; zcta10</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2776,7 +2776,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>208682</t>
+          <t>208684</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2786,33 +2786,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Retail Establishments by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Law Enforcement by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>V2.0</t>
+          <t>V2.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4/9/2026</t>
+          <t>4/7/2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10.3886/E208682V20</t>
+          <t>10.3886/E208684V22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10.3886/E208682</t>
+          <t>10.3886/E208684</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208682</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208684</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>retail_establishments</t>
+          <t>law_enforcement</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>retail_1990-2022</t>
+          <t>lawenf_1990-2022</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2855,7 +2855,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>208684</t>
+          <t>208751</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2865,48 +2865,48 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Law Enforcement by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Eating and Drinking Places by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>V2.2</t>
+          <t>V2.0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4/7/2026</t>
+          <t>4/8/2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10.3886/E208684V22</t>
+          <t>10.3886/E208751V20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>10.3886/E208684</t>
+          <t>10.3886/E208751</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208684</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208751</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Robert Melendez; Philippa J. Clarke; Grace A. Noppert; Lindsay Gypin; William Milton Clary II</t>
+          <t>Robert Melendez; William Milton Clary II; Philippa J. Clarke; Grace A. Noppert; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>law_enforcement</t>
+          <t>eating_drinking</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>lawenf_1990-2022</t>
+          <t>eatdrink_1990-2022</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2934,7 +2934,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>208751</t>
+          <t>208906</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eating and Drinking Places by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Personal Care Services and Laundry by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>V2.0</t>
+          <t>V2.3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2959,33 +2959,33 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>10.3886/E208751V20</t>
+          <t>10.3886/E208906V23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10.3886/E208751</t>
+          <t>10.3886/E208906</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208751</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208906</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Robert Melendez; William Milton Clary II; Philippa J. Clarke; Grace A. Noppert; Lindsay Gypin</t>
+          <t>Robert Melendez; Philippa J. Clarke; Grace A. Noppert; Lindsay Gypin; William Milton Clary II</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>eating_drinking</t>
+          <t>personal_care_laundromats</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>eatdrink_1990-2022</t>
+          <t>pclaund_tractZCTA_1990-2022</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3013,7 +3013,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>208906</t>
+          <t>208907</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3023,48 +3023,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Personal Care Services and Laundry by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Liquor, Tobacco, Cannabis, Vape, and Convenience Stores by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>V2.3</t>
+          <t>V2.0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4/8/2026</t>
+          <t>4/9/2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10.3886/E208906V23</t>
+          <t>10.3886/E208907V20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10.3886/E208906</t>
+          <t>10.3886/E208907</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208906</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208907</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Robert Melendez; Philippa J. Clarke; Grace A. Noppert; Lindsay Gypin; William Milton Clary II</t>
+          <t>Robert Melendez; William Milton Clary II; Philippa J. Clarke; Grace A. Noppert; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>personal_care_laundromats</t>
+          <t>liquor_tobacco_convenience</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>pclaund_tractZCTA_1990-2022</t>
+          <t>lqtbcan_tractZCTA_1990-2022</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3092,7 +3092,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>208907</t>
+          <t>209050</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3102,33 +3102,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Liquor, Tobacco, Cannabis, Vape, and Convenience Stores by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Healthcare Services by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>V2.0</t>
+          <t>V2.1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4/9/2026</t>
+          <t>3/31/2026</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>10.3886/E208907V20</t>
+          <t>10.3886/E209050V21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10.3886/E208907</t>
+          <t>10.3886/E209050</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/208907</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/209050</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>liquor_tobacco_convenience</t>
+          <t>health_care_nets</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>lqtbcan_tractZCTA_1990-2022</t>
+          <t>health_care_nets_1990-2022</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3171,7 +3171,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>209050</t>
+          <t>209163</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3181,33 +3181,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Healthcare Services by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Arts, Entertainment, and Leisure Establishments by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>V2.1</t>
+          <t>V3.0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3/31/2026</t>
+          <t>4/17/2026</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10.3886/E209050V21</t>
+          <t>10.3886/E209163V30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10.3886/E209050</t>
+          <t>10.3886/E209163</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/209050</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/209163</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>health_care_nets</t>
+          <t>arts_entertainment_recreation</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>health_care_nets_1990-2022</t>
+          <t>artsentleisure_1990-2022</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3250,7 +3250,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>209163</t>
+          <t>209164</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Arts, Entertainment, and Leisure Establishments by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Recreational Establishments by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3270,38 +3270,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4/17/2026</t>
+          <t>4/9/2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10.3886/E209163V30</t>
+          <t>10.3886/E209164V30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10.3886/E209163</t>
+          <t>10.3886/E209164</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/209163</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/209164</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Robert Melendez; William Milton Clary II; Philippa J. Clarke; Grace A. Noppert; Ellis Dyke</t>
+          <t>Robert Melendez; William Milton Clary II; Philippa J. Clarke; Grace A. Noppert; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>arts_entertainment_recreation</t>
+          <t>recreation</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>artsentleisure_1990-2022</t>
+          <t>recreation_1990-2022</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3329,7 +3329,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>209164</t>
+          <t>209313</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3339,33 +3339,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Recreational Establishments by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Grocery and Food Stores by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>V3.0</t>
+          <t>V2.0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4/9/2026</t>
+          <t>4/8/2026</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10.3886/E209164V30</t>
+          <t>10.3886/E209313V20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>10.3886/E209164</t>
+          <t>10.3886/E209313</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/209164</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/209313</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>recreation</t>
+          <t>grocery_stores</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>recreation_1990-2022</t>
+          <t>grocery_1990-2022</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3408,7 +3408,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>209313</t>
+          <t>209324</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3418,33 +3418,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Grocery and Food Stores by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Dollar Stores by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>V2.0</t>
+          <t>V2.1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4/8/2026</t>
+          <t>3/31/2026</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>10.3886/E209313V20</t>
+          <t>10.3886/E209324V21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10.3886/E209313</t>
+          <t>10.3886/E209324</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/209313</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/209324</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>grocery_stores</t>
+          <t>dollar_stores</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>grocery_1990-2022</t>
+          <t>dollar_stores_1990-2022</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3487,7 +3487,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>209324</t>
+          <t>210581</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3497,68 +3497,64 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dollar Stores by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Standardized Area Deprivation Index by Census Block Group, United States, 2015, 2020 and 2022</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>V2.1</t>
+          <t>V1.9</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3/31/2026</t>
+          <t>11/8/2024</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>10.3886/E209324V21</t>
+          <t>10.3886/E210581V19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>10.3886/E209324</t>
+          <t>10.3886/E210581</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/209324</t>
+          <t>https://www.openicpsr.org/openicpsr/project/210581/view</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Robert Melendez; William Milton Clary II; Philippa J. Clarke; Grace A. Noppert; Lindsay Gypin</t>
+          <t>Kimberly Rollings; Robert Melendez; Philippa Clarke; Clemens Noelke; Robert Ressler; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>dollar_stores</t>
+          <t>ADI_standardized</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>dollar_stores_1990-2022</t>
+          <t>ADI_standardized</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>1990-2022</t>
-        </is>
-      </c>
+          <t>Block Group</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
+          <t>blkgrp_fips10; blkgrp_fips20</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Census Tract</t>
+          <t>Block Group</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr"/>
@@ -3566,74 +3562,82 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>210581</t>
+          <t>220701</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>alternate-deposit</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Standardized Area Deprivation Index by Census Block Group, United States, 2015, 2020 and 2022</t>
+          <t>Land Cover by Census Tract and ZIP Code Tabulation Area, United States, 1985- 2023</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>V1.9</t>
+          <t>V1.4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>11/8/2024</t>
+          <t>2/25/2025</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10.3886/E210581V19</t>
+          <t>10.3886/E220701V14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10.3886/E210581</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>10.3886/E220701</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>10.3886/ICPSR38598.v2</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.openicpsr.org/openicpsr/project/210581/view</t>
+          <t>https://www.openicpsr.org/openicpsr/project/220701/view</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Kimberly Rollings; Robert Melendez; Philippa Clarke; Clemens Noelke; Robert Ressler; Lindsay Gypin</t>
+          <t>Robert Melendez; Philippa Clarke; Longrong Pan; Grace Noppert; Lindsay Gypin; Mao Li; Anam Khan; Iris Gomez-Lopez; Megan Chenoweth</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>ADI_standardized</t>
+          <t>land_cover</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ADI_standardized</t>
+          <t>landcover_1985-2023</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Block Group</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1985-2023</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>blkgrp_fips10; blkgrp_fips20</t>
+          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Block Group</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
@@ -3641,62 +3645,58 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>220701</t>
+          <t>222263</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>alternate-deposit</t>
+          <t>current</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Land Cover by Census Tract and ZIP Code Tabulation Area, United States, 1985- 2023</t>
+          <t>Ophthalmologists by Census Tract and ZCTA, United States, 1990-2021</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>V1.4</t>
+          <t>V1.2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2/25/2025</t>
+          <t>3/10/2025</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>10.3886/E220701V14</t>
+          <t>10.3886/E222263V12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10.3886/E220701</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>10.3886/ICPSR38598.v2</t>
-        </is>
-      </c>
+          <t>10.3886/E222263</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.openicpsr.org/openicpsr/project/220701/view</t>
+          <t>https://www.openicpsr.org/openicpsr/project/222263/view</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Robert Melendez; Philippa Clarke; Longrong Pan; Grace Noppert; Lindsay Gypin; Mao Li; Anam Khan; Iris Gomez-Lopez; Megan Chenoweth</t>
+          <t>Robert Melendez; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>land_cover</t>
+          <t>opthamologists</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>landcover_1985-2023</t>
+          <t>opthamologists</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1985-2023</t>
+          <t>1990-2021</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3724,58 +3724,62 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>222263</t>
+          <t>222901</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>alternate-deposit</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ophthalmologists by Census Tract and ZCTA, United States, 1990-2021</t>
+          <t>Hospitals by Census Tract and ZCTA, 2023</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>V1.2</t>
+          <t>V1.3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3/10/2025</t>
+          <t>3/14/2025</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10.3886/E222263V12</t>
+          <t>10.3886/E222901V13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>10.3886/E222263</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>10.3886/E222901</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>10.3886/ICPSR39378.v1</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.openicpsr.org/openicpsr/project/222263/view</t>
+          <t>https://www.openicpsr.org/openicpsr/project/222901/view</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Robert Melendez; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
+          <t>Longrong Pan; Robert Melendez; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>opthamologists</t>
+          <t>hospitals</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>opthamologists</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3785,12 +3789,12 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>1990-2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
+          <t>tract_fips10; tract_fips20; zcta10; zcta20</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3803,77 +3807,73 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>222901</t>
+          <t>230941</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>alternate-deposit</t>
+          <t>current</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hospitals by Census Tract and ZCTA, 2023</t>
+          <t>PRISM Climate of Census Tracts, United States, 1981-2024</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>V1.3</t>
+          <t>V2.5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3/14/2025</t>
+          <t>8/4/2025</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10.3886/E222901V13</t>
+          <t>10.3886/E230941V25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10.3886/E222901</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>10.3886/ICPSR39378.v1</t>
-        </is>
-      </c>
+          <t>10.3886/E230941</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.openicpsr.org/openicpsr/project/222901/view</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/230941</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Longrong Pan; Robert Melendez; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
+          <t>Carina J. Gronlund; Philippa J. Clarke; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>hospitals</t>
+          <t>PRISM</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>ppt; tmax</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
+          <t>Census Tract (2010, 2020)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2000-2009; 2010-2019</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>tract_fips10; tract_fips20; zcta10; zcta20</t>
+          <t>year; tract_fips10; tract_fips20</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -3881,12 +3881,16 @@
           <t>Census Tract</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>MULTI_SUBFOLDER</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>230941</t>
+          <t>237305</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3896,63 +3900,59 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PRISM Climate of Census Tracts, United States, 1981-2024</t>
+          <t>Air Conditioning Probability by Census Tract, United States, 2016</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>V2.5</t>
+          <t>V1.1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8/4/2025</t>
+          <t>8/21/2025</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10.3886/E230941V25</t>
+          <t>10.3886/E237305V11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>10.3886/E230941</t>
+          <t>10.3886/E237305</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.openicpsr.org/openicpsr/project/230941/view</t>
+          <t>https://www.openicpsr.org/openicpsr/project/237305/view</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Carina Gronlund; Philippa Clarke; Lindsay Gypin</t>
+          <t>Carina Gronlund; Robert Melendez; Philippa Clarke; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>PRISM</t>
+          <t>air_conditioning</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ppt; tmax</t>
+          <t>air_conditioning</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020)</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>2000-2009; 2010-2019</t>
-        </is>
-      </c>
+          <t>Census Tract (2010)</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>year; tract_fips10; tract_fips20</t>
+          <t>tract_fips10</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -3960,16 +3960,12 @@
           <t>Census Tract</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>MULTI_SUBFOLDER</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>237305</t>
+          <t>301419</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3979,7 +3975,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Air Conditioning Probability by Census Tract, United States, 2016</t>
+          <t>Essential Businesses in Census Tracts or ZIP Code Tabulation Areas, United States, 2020</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3989,49 +3985,57 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8/21/2025</t>
+          <t>1/12/2026</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10.3886/E237305V11</t>
+          <t>10.3886/E301419V11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>10.3886/E237305</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>10.3886/ICPSR301419.v1</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>10.3886/ICPSR301419.v1</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.openicpsr.org/openicpsr/project/237305/view</t>
+          <t>https://archive.icpsr.umich.edu/view/studies/301419/versions/V1.1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Carina Gronlund; Robert Melendez; Philippa Clarke; Lindsay Gypin</t>
+          <t>Robert Melendez; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>air_conditioning</t>
+          <t>essential_businesses</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>air_conditioning</t>
+          <t>essential_businesses</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>tract_fips10</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4044,7 +4048,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>301419</t>
+          <t>302178</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4054,67 +4058,67 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Essential Businesses in Census Tracts or ZIP Code Tabulation Areas, United States, 2020</t>
+          <t>Essential Workers by Census Tract and ZIP Code Tabulation Area, United States, 2018-2022</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>V1.1</t>
+          <t>V1.0</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1/12/2026</t>
+          <t>1/29/2026</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>10.3886/E301419V11</t>
+          <t>10.3886/E302178V10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>10.3886/ICPSR301419.v1</t>
+          <t>10.3886/ICPSR302178.v1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>10.3886/ICPSR301419.v1</t>
+          <t>10.3886/ICPSR302178.v1</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://archive.icpsr.umich.edu/view/studies/301419/versions/V1.1</t>
+          <t>https://archive.icpsr.umich.edu/view/studies/302178/versions/V1.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Robert Melendez; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
+          <t>Kate Duchowny; Robert Melendez; Grace Noppert; Philippa Clarke; Lindsay Gypin; William Milton Clary II</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>essential_businesses</t>
+          <t>essential_workers</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>essential_businesses</t>
+          <t>ewrkr_2018-2022</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
+          <t>Census Tract (2020, 2022); ZCTA (2020)</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018-2022</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
+          <t>tract_fips20; tract_fips22; zcta_fips20</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4127,7 +4131,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>302178</t>
+          <t>302343</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4137,67 +4141,59 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Essential Workers by Census Tract and ZIP Code Tabulation Area, United States, 2018-2022</t>
+          <t>Training and Vocation Schools by Census Tract and ZCTA, United States, 1990-2022</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>V1.0</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>1/29/2026</t>
-        </is>
-      </c>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>10.3886/E302178V10</t>
+          <t>10.3886/ICPSR302343.v1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>10.3886/ICPSR302178.v1</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>10.3886/ICPSR302178.v1</t>
-        </is>
-      </c>
+          <t>10.3886/ICPSR302343.v1</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://archive.icpsr.umich.edu/view/studies/302178/versions/V1.0</t>
+          <t>https://www.icpsr.umich.edu/sites/icpsr/view/studies/302343/versions/V1.3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Kate Duchowny; Robert Melendez; Grace Noppert; Philippa Clarke; Lindsay Gypin; William Milton Clary II</t>
+          <t>Robert Melendez; William Milton Clary II; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>essential_workers</t>
+          <t>training_vocation</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ewrkr_2018-2022</t>
+          <t>training_vocation_1990-2022</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Census Tract (2020, 2022); ZCTA (2020)</t>
+          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2018-2022</t>
+          <t>1990-2022</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>tract_fips20; tract_fips22; zcta_fips20</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -4210,7 +4206,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>302343</t>
+          <t>302937</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4220,7 +4216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Training and Vocation Schools by Census Tract and ZCTA, United States, 1990-2022</t>
+          <t>Broadband Availability by Census Tract and ZIP Code Tabulation Area (ZCTA) United States, 2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4231,48 +4227,48 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>10.3886/ICPSR302343.v1</t>
+          <t>10.3886/ICPSR302937.v1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>10.3886/ICPSR302343.v1</t>
+          <t>10.3886/ICPSR302937.v1</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/icpsr/view/studies/302343/versions/V1.3</t>
+          <t>https://www.icpsr.umich.edu/sites/icpsr/view/studies/302937/versions/V1.1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Robert Melendez; William Milton Clary II; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
+          <t>Robert Melendez; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>training_vocation</t>
+          <t>broadband</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>training_vocation_1990-2022</t>
+          <t>broadband_tract_zcta_2025</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
+          <t>Census Tract (2020, 2022); ZCTA (2020)</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1990-2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
+          <t>tract_fips20; tract_fips22; zcta20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4285,7 +4281,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>302937</t>
+          <t>305511</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4295,7 +4291,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Broadband Availability by Census Tract and ZIP Code Tabulation Area (ZCTA) United States, 2025</t>
+          <t>Parks and Proximity to Polluting Sites by Census Tract and ZIP Code Tabulation Area (ZCTA), United States, 2024</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4303,36 +4299,40 @@
           <t>V1</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>5/12/2026</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>10.3886/ICPSR302937.v1</t>
+          <t>10.3886/ICPSR305511.v1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>10.3886/ICPSR302937.v1</t>
+          <t>10.3886/ICPSR305511.v1</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/icpsr/view/studies/302937/versions/V1.1</t>
+          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/305511/versions/V1.1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Robert Melendez; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
+          <t>Elliott Chemberlin; Robert Melendez; Kate Duchowny; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>broadband</t>
+          <t>parks</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>broadband_tract_zcta_2025</t>
+          <t>parks_tractzcta_2024</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4360,73 +4360,69 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>305511</t>
+          <t>110663</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>superseded</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Parks and Proximity to Polluting Sites by Census Tract and ZIP Code Tabulation Area (ZCTA), United States, 2024</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>5/12/2026</t>
-        </is>
-      </c>
+          <t>Land Cover by Census Tract, United States, 2001-2016</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>10.3886/ICPSR305511.v1</t>
+          <t>10.3886/E110663V10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>10.3886/ICPSR305511.v1</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>10.3886/E110663</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>10.3886/ICPSR38598.v2</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://www.icpsr.umich.edu/sites/nanda/view/studies/305511/versions/V1.1</t>
+          <t>https://www.openicpsr.org/openicpsr/project/110663</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Elliott Chemberlin; Robert Melendez; Kate Duchowny; Philippa Clarke; Grace Noppert; Lindsay Gypin</t>
+          <t>Philippa Clarke; Robert Melendez</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>parks</t>
+          <t>land_cover</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>parks_tractzcta_2024</t>
+          <t>landcover_tract_2001-2016</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Census Tract (2020, 2022); ZCTA (2020)</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2001-2016</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>tract_fips20; tract_fips22; zcta20</t>
+          <t>tract_fips</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4447,7 +4443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N147"/>
+  <dimension ref="A1:N155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9809,37 +9805,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>recreation</t>
+          <t>public_transit_quality</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>recreation_1990-2021</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>1990-2021</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>1990-2021</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>1990-2021</t>
-        </is>
-      </c>
+          <t>Census Tract (2020, 2022)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
+          <t>tract_fips20; tract_fips22</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9854,7 +9838,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -9877,58 +9861,38 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>recreation</t>
+          <t>public_transit_quality</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>recreation_1990-2022</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1990-2022</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>1990-2022</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>1990-2022</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Census Tract</t>
-        </is>
-      </c>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9941,37 +9905,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>religious_civic_social_orgs</t>
+          <t>public_transit_quality</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>relcivsoc_1990-2021</t>
+          <t>Adjacency</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1990-2021</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>1990-2021</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>1990-2021</t>
-        </is>
-      </c>
+          <t>Census Tract (2020, 2022)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
+          <t>tract_fips20; tract_fips22</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9981,12 +9933,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -9996,7 +9948,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -10009,58 +9961,38 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>religious_civic_social_orgs</t>
+          <t>public_transit_quality</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>relcivsoc_1990-2022</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>1990-2022</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>1990-2022</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>1990-2022</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Census Tract</t>
-        </is>
-      </c>
+          <t>Affordability</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -10073,37 +10005,25 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>religious_civic_social_orgs</t>
+          <t>public_transit_quality</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>relcivsoc_tract_2003-2017</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>2003-2017</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2003-2017</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2003-2017</t>
-        </is>
-      </c>
+          <t>Census Tract (2020, 2022)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>tract_fips10; year</t>
+          <t>tract_fips20; tract_fips22</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -10118,7 +10038,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -10128,7 +10048,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -10141,58 +10061,38 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>religious_civic_social_orgs</t>
+          <t>public_transit_quality</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>relcivsoc_tract_2006-2015</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Census Tract (2010)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2006-2015</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2006-2015</t>
-        </is>
-      </c>
+          <t>TransitFunding</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>tract_fips10</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Census Tract</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10205,17 +10105,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>religious_civic_social_orgs</t>
+          <t>recreation</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>relcivsoc_zcta10_1990-2021</t>
+          <t>recreation_1990-2021</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ZCTA (2010)</t>
+          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -10228,31 +10128,39 @@
           <t>1990-2021</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1990-2021</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>zcta10; year</t>
+          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10265,62 +10173,58 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>religious_civic_social_orgs</t>
+          <t>recreation</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>relcivsoc_zcta_2003-2017</t>
+          <t>recreation_1990-2022</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ZCTA (2019)</t>
+          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2003-2017</t>
+          <t>1990-2022</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2003-2017</t>
+          <t>1990-2022</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2003-2017</t>
+          <t>1990-2022</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>zcta19; year</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10333,12 +10237,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>retail_establishments</t>
+          <t>religious_civic_social_orgs</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>retail_1990-2021</t>
+          <t>relcivsoc_1990-2021</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -10363,7 +10267,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>year; tract_fips20; zcta10; zcta20</t>
+          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10373,12 +10277,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>192</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -10401,12 +10305,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>retail_establishments</t>
+          <t>religious_civic_social_orgs</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>retail_1990-2022</t>
+          <t>relcivsoc_1990-2022</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -10446,7 +10350,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>194</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -10465,12 +10369,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>retail_establishments</t>
+          <t>religious_civic_social_orgs</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>retail_tract_2003-2017</t>
+          <t>relcivsoc_tract_2003-2017</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10510,7 +10414,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -10533,12 +10437,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>retail_establishments</t>
+          <t>religious_civic_social_orgs</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>retail_tract_2006-2015</t>
+          <t>relcivsoc_tract_2006-2015</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10569,12 +10473,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -10597,37 +10501,33 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>retail_establishments</t>
+          <t>religious_civic_social_orgs</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>retail_zcta_2003-2017</t>
+          <t>relcivsoc_zcta10_1990-2021</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ZCTA (2019)</t>
+          <t>ZCTA (2010)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2003-2017</t>
+          <t>1990-2021</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2003-2017</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2003-2017</t>
-        </is>
-      </c>
+          <t>1990-2021</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>zcta19; year</t>
+          <t>zcta10; year</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -10637,22 +10537,18 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10665,48 +10561,52 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>schools</t>
+          <t>religious_civic_social_orgs</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>neighborhood_school_gap_tract_0910_1516</t>
+          <t>relcivsoc_zcta_2003-2017</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
+          <t>ZCTA (2019)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2009-2016</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
+          <t>2003-2017</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2003-2017</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2009-2016</t>
+          <t>2003-2017</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>tract_fips10; year</t>
+          <t>zcta19; year</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Census Tract</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -10716,7 +10616,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -10729,33 +10629,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>schools</t>
+          <t>retail_establishments</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>neighborhood_school_gap_tract_supp_0910_1516</t>
+          <t>retail_1990-2021</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
+          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2009-2010</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>1990-2021</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1990-2021</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2009-2010</t>
+          <t>1990-2021</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>tract_fips10; year</t>
+          <t>year; tract_fips20; zcta10; zcta20</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10765,12 +10669,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>159</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -10780,7 +10684,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10793,58 +10697,58 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>schools</t>
+          <t>retail_establishments</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>neighborhood_school_gap_zcta_0910_1516</t>
+          <t>retail_1990-2022</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ZCTA (2019)</t>
+          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2009-2016</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
+          <t>1990-2022</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1990-2022</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2009-2016</t>
+          <t>1990-2022</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>zcta19; year</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -10857,48 +10761,52 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>schools</t>
+          <t>retail_establishments</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>neighborhood_school_gap_zcta_supp_0910_1516</t>
+          <t>retail_tract_2003-2017</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ZCTA (2019)</t>
+          <t>Census Tract (2010)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2009-2010</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
+          <t>2003-2017</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2003-2017</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2009-2010</t>
+          <t>2003-2017</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>zcta19; year</t>
+          <t>tract_fips10; year</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -10908,7 +10816,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -10921,12 +10829,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>schools</t>
+          <t>retail_establishments</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>school_counts_tract_2000-2018</t>
+          <t>retail_tract_2006-2015</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -10936,22 +10844,18 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2000-2018</t>
+          <t>2006-2015</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2000-2018</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2000-2018</t>
-        </is>
-      </c>
+          <t>2006-2015</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>tract_fips10; year</t>
+          <t>tract_fips10</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -10961,12 +10865,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>312</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -10989,12 +10893,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>schools</t>
+          <t>retail_establishments</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>school_counts_zcta_2000-2018</t>
+          <t>retail_zcta_2003-2017</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11004,17 +10908,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2000-2018</t>
+          <t>2003-2017</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2000-2018</t>
+          <t>2003-2017</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2000-2018</t>
+          <t>2003-2017</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -11034,7 +10938,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -11062,47 +10966,43 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>schools_district_2000-2018</t>
+          <t>neighborhood_school_gap_tract_0910_1516</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>School District</t>
+          <t>Census Tract (2010)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2000-2018</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>2000-2018</t>
-        </is>
-      </c>
+          <t>2009-2016</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2000-2018</t>
+          <t>2009-2016</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>leaid; year</t>
+          <t>tract_fips10; year</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>School District</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -11112,7 +11012,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -11125,33 +11025,33 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ses_demographics</t>
+          <t>schools</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>sesdem_2018-2022</t>
+          <t>neighborhood_school_gap_tract_supp_0910_1516</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020); ZCTA (2020)</t>
+          <t>Census Tract (2010)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2018-2022</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>2018-2022</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
+          <t>2009-2010</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2009-2010</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>tract_fips10; tract_fips20; zcta20</t>
+          <t>tract_fips10; year</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11161,18 +11061,22 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -11185,54 +11089,58 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ses_demographics</t>
+          <t>schools</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>sesdem_tract_1990</t>
+          <t>neighborhood_school_gap_zcta_0910_1516</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
+          <t>ZCTA (2019)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
+          <t>2009-2016</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2009-2016</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>tract_fips10</t>
+          <t>zcta19; year</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Census Tract</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -11245,48 +11153,48 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ses_demographics</t>
+          <t>schools</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>sesdem_tract_1990-2010</t>
+          <t>neighborhood_school_gap_zcta_supp_0910_1516</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
+          <t>ZCTA (2019)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1990-2010</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>1990-2010</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
+          <t>2009-2010</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2009-2010</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>tract_fips10</t>
+          <t>zcta19; year</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Census Tract</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>192</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -11309,12 +11217,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ses_demographics</t>
+          <t>schools</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>sesdem_tract_2000-2010</t>
+          <t>school_counts_tract_2000-2018</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -11324,18 +11232,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2000-2010</t>
+          <t>2000-2018</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2000-2010</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
+          <t>2000-2018</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2000-2018</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>tract_fips10</t>
+          <t>tract_fips10; year</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -11345,12 +11257,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -11360,7 +11272,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -11373,48 +11285,52 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ses_demographics</t>
+          <t>schools</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>sesdem_tract_2008-2017</t>
+          <t>school_counts_zcta_2000-2018</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
+          <t>ZCTA (2019)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2008-2017</t>
+          <t>2000-2018</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2008-2017</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+          <t>2000-2018</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2000-2018</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>tract_fips10</t>
+          <t>zcta19; year</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Census Tract</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -11424,7 +11340,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -11437,38 +11353,42 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ses_demographics</t>
+          <t>schools</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>sesdem_tract_2016-2020</t>
+          <t>schools_district_2000-2018</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Census Tract (2020)</t>
+          <t>School District</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>2000-2018</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2016-2020</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
+          <t>2000-2018</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2000-2018</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>tract_fips20</t>
+          <t>leaid; year</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Census Tract</t>
+          <t>School District</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -11478,7 +11398,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -11488,7 +11408,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -11506,53 +11426,49 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>sesdem_zcta_2008-2017</t>
+          <t>sesdem_2018-2022</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ZCTA (2010)</t>
+          <t>Census Tract (2010, 2020); ZCTA (2020)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2008-2017</t>
+          <t>2018-2022</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2008-2017</t>
+          <t>2018-2022</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>zcta10</t>
+          <t>tract_fips10; tract_fips20; zcta20</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -11570,43 +11486,43 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>sesdem_zcta_2016-2020</t>
+          <t>sesdem_2019-2023</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ZCTA (2020)</t>
+          <t>Census Tract (2010, 2020, 2022); ZCTA (2020)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>2019-2023</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>2019-2023</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>zcta20</t>
+          <t>tract_fips10; tract_fips20; tract_fips22; zcta20</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>296</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -11616,7 +11532,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -11634,49 +11550,53 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>totpop_zcta_2000-2010</t>
+          <t>sesdem_2020-2024</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ZCTA (2010)</t>
+          <t>Census Tract (2010, 2020, 2022); ZCTA (2020)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2000-2010</t>
+          <t>2020-2024</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2000-2010</t>
+          <t>2020-2024</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>zcta10</t>
+          <t>tract_fips10; tract_fips20; tract_fips22; zcta20</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -11689,37 +11609,33 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>social_services</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>social_services_1990-2021</t>
+          <t>sesdem_tract_1990</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
+          <t>Census Tract (2010)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1990-2021</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1990-2021</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>1990-2021</t>
-        </is>
-      </c>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
+          <t>tract_fips10</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -11729,22 +11645,18 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -11757,37 +11669,33 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>social_services</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>social_services_1990-2022</t>
+          <t>sesdem_tract_1990-2010</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
+          <t>Census Tract (2010)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1990-2022</t>
+          <t>1990-2010</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1990-2022</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>1990-2022</t>
-        </is>
-      </c>
+          <t>1990-2010</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
+          <t>tract_fips10</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -11797,18 +11705,22 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -11821,12 +11733,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>social_services</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>social_services_tract_2003-2017</t>
+          <t>sesdem_tract_2000-2010</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -11836,22 +11748,18 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2003-2017</t>
+          <t>2000-2010</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2003-2017</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2003-2017</t>
-        </is>
-      </c>
+          <t>2000-2010</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>tract_fips10; year</t>
+          <t>tract_fips10</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -11861,12 +11769,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>706</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -11876,7 +11784,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -11889,12 +11797,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>social_services</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>social_services_tract_2006-2015</t>
+          <t>sesdem_tract_2008-2017</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -11904,12 +11812,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2006-2015</t>
+          <t>2008-2017</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2006-2015</t>
+          <t>2008-2017</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -11930,7 +11838,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>198</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -11940,7 +11848,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -11953,42 +11861,38 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>social_services</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>social_services_zcta_2003-2017</t>
+          <t>sesdem_tract_2016-2020</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ZCTA (2019)</t>
+          <t>Census Tract (2020)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2003-2017</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2003-2017</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2003-2017</t>
-        </is>
-      </c>
+          <t>2016-2020</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>zcta19; year</t>
+          <t>tract_fips20</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11998,7 +11902,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -12008,7 +11912,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -12021,48 +11925,48 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>street_connectivity</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>street_connectivity_tract_2010</t>
+          <t>sesdem_zcta_2008-2017</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
+          <t>ZCTA (2010)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2008-2017</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2008-2017</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>tract_fips10</t>
+          <t>zcta10</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Census Tract</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -12072,7 +11976,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -12085,101 +11989,97 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>street_connectivity</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>street_connectivity_tract_2020</t>
+          <t>sesdem_zcta_2016-2020</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Census Tract (2020)</t>
+          <t>ZCTA (2020)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>tract_fips20</t>
+          <t>zcta20</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Census Tract</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>nanda_stconnect_tract_2020_01_data_dictionary.xlsx: BadZipFile: File is not a zip file</t>
-        </is>
-      </c>
+      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>street_connectivity</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>street_connectivity_zcta_2010</t>
+          <t>totpop_zcta_2000-2010</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>ZCTA (2010)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000-2010</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2000-2010</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>zcta</t>
+          <t>zcta10</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -12194,14 +12094,10 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>1</t>
@@ -12217,48 +12113,52 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>street_connectivity</t>
+          <t>social_services</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>street_connectivity_zcta_2020</t>
+          <t>social_services_1990-2021</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract (2010, 2020); ZCTA (2010, 2020)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1990-2021</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
+          <t>1990-2021</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1990-2021</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>zcta</t>
+          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>285</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -12268,7 +12168,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -12281,33 +12181,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>social_services</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>street_type_tract_2010</t>
+          <t>social_services_1990-2022</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
+          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1990-2022</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
+          <t>1990-2022</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1990-2022</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>tract_fips10</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -12317,22 +12221,18 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -12345,33 +12245,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>social_services</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>street_type_tract_2020</t>
+          <t>social_services_tract_2003-2017</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Census Tract (2020)</t>
+          <t>Census Tract (2010)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2003-2017</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
+          <t>2003-2017</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2003-2017</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>tract_fips20</t>
+          <t>tract_fips10; year</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -12381,18 +12285,22 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -12405,48 +12313,48 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>social_services</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>street_type_zcta_2010</t>
+          <t>social_services_tract_2006-2015</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract (2010)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2006-2015</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2006-2015</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>zcta</t>
+          <t>tract_fips10</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>218</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -12469,33 +12377,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>social_services</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>street_type_zcta_2020</t>
+          <t>social_services_zcta_2003-2017</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ZCTA (2020)</t>
+          <t>ZCTA (2019)</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2003-2017</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
+          <t>2003-2017</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2003-2017</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>zcta20</t>
+          <t>zcta19; year</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -12505,18 +12417,22 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -12529,52 +12445,48 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>street_connectivity</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>traffic_volume_interpolated_zcta_1963-2019</t>
+          <t>street_connectivity_tract_2010</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ZCTA (2019)</t>
+          <t>Census Tract (2010)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>1963-2019</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1963-2019</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>1963-2019</t>
-        </is>
-      </c>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>zcta19; year</t>
+          <t>tract_fips10</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ZCTA</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -12584,7 +12496,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -12597,37 +12509,33 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>street_connectivity</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>traffic_volume_noninterpolated_tract_1963-2019</t>
+          <t>street_connectivity_tract_2020</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
+          <t>Census Tract (2020)</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>1963-2019</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1963-2019</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>1963-2019</t>
-        </is>
-      </c>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>tract_fips10; year</t>
+          <t>tract_fips20</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -12637,12 +12545,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -12652,7 +12560,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -12660,42 +12568,42 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>nanda_stconnect_tract_2020_01_data_dictionary.xlsx: BadZipFile: File is not a zip file</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>street_connectivity</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>traffic_volume_noninterpolated_zcta_1963-2019</t>
+          <t>street_connectivity_zcta_2010</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ZCTA (2019)</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>1963-2019</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1963-2019</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>1963-2019</t>
-        </is>
-      </c>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>zcta19; year</t>
+          <t>zcta</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -12710,10 +12618,14 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>1</t>
@@ -12729,52 +12641,48 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>training_vocation</t>
+          <t>street_connectivity</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>training_vocation_1990-2022</t>
+          <t>street_connectivity_zcta_2020</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>1990-2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>1990-2022</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>1990-2022</t>
-        </is>
-      </c>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
+          <t>zcta</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Census Tract</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -12784,7 +12692,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -12797,17 +12705,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>urbanicity</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>urbanicity_ruca_zip_2010</t>
+          <t>street_type_tract_2010</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>Census Tract (2010)</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -12823,28 +12731,32 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>zip_code</t>
+          <t>tract_fips10</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ZIP</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -12857,33 +12769,33 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>urbanicity</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>urbanicity_tract_2010</t>
+          <t>street_type_tract_2020</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Census Tract (2010)</t>
+          <t>Census Tract (2020)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>tract_fips10; tract_fips</t>
+          <t>tract_fips20</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -12898,14 +12810,10 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>2</t>
@@ -12921,42 +12829,38 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>voting</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>voting_county_2004-2018</t>
+          <t>street_type_zcta_2010</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2004-2018</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2004-2018</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2000-2018</t>
-        </is>
-      </c>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>stcofips; year</t>
+          <t>zcta</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -12966,7 +12870,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -12976,7 +12880,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -12989,36 +12893,48 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>voting</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>voting_county_2004-2022</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>street_type_zcta_2020</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ZCTA (2020)</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2004-2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2004-2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>zcta20</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>ZCTA</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -13029,7 +12945,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>NO_DICT</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
@@ -13037,54 +12953,62 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>voting</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>voting_county_2018-2022</t>
+          <t>traffic_volume_interpolated_zcta_1963-2019</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>County (2020)</t>
+          <t>ZCTA (2019)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2018-2022</t>
+          <t>1963-2019</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2018-2022</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
+          <t>1963-2019</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>1963-2019</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>stcofips20; year</t>
+          <t>zcta19; year</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -13097,54 +13021,62 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>cold_days_p1_county_2002-2016</t>
+          <t>traffic_volume_noninterpolated_tract_1963-2019</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>County (2010)</t>
+          <t>Census Tract (2010)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>1963-2019</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2002-2016</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
+          <t>1963-2019</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1963-2019</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>stcofips10</t>
+          <t>tract_fips10; year</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
@@ -13157,38 +13089,42 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>cold_days_p5_county_2002-2016</t>
+          <t>traffic_volume_noninterpolated_zcta_1963-2019</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>County (2010)</t>
+          <t>ZCTA (2019)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>1963-2019</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2002-2016</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
+          <t>1963-2019</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1963-2019</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>stcofips10</t>
+          <t>zcta19; year</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>ZCTA</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -13198,13 +13134,13 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -13217,54 +13153,62 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>training_vocation</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>cold_days_precip_county_2002-2016</t>
+          <t>training_vocation_1990-2022</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>County (2010)</t>
+          <t>Census Tract (2010, 2020, 2022); ZCTA (2010, 2020)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>1990-2022</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2002-2016</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
+          <t>1990-2022</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>1990-2022</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>stcofips10</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -13277,54 +13221,54 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>urbanicity</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>freezing_days_county_2002-2016</t>
+          <t>urbanicity_ruca_zip_2010</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>County (2010)</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>stcofips10</t>
+          <t>zip_code</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>ZIP</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -13337,54 +13281,58 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>urbanicity</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>freezing_days_precip_county_2002-2016</t>
+          <t>urbanicity_tract_2010</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>County (2010)</t>
+          <t>Census Tract (2010)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>stcofips10</t>
+          <t>tract_fips10; tract_fips</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>County</t>
+          <t>Census Tract</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -13397,33 +13345,37 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>voting</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>hot_days_p95_county_2002-2016</t>
+          <t>voting_county_2004-2018</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>County (2010)</t>
+          <t>County</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>2004-2018</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2002-2016</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
+          <t>2004-2018</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2000-2018</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>stcofips10</t>
+          <t>stcofips; year</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -13438,13 +13390,17 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -13457,23 +13413,23 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>voting</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>hot_days_p99_county_2002-2016</t>
+          <t>voting_county_2004-2022</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>2004-2022</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>2004-2022</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
@@ -13492,7 +13448,7 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -13505,33 +13461,33 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>voting</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>rainsnow_county_2002-2016</t>
+          <t>voting_county_2018-2022</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>County (2010)</t>
+          <t>County (2020)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>2018-2022</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2002-2016</t>
+          <t>2018-2022</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>stcofips10</t>
+          <t>stcofips20; year</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -13541,18 +13497,18 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13570,7 +13526,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>rainy_days_county_2002-2016</t>
+          <t>cold_days_p1_county_2002-2016</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -13601,12 +13557,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>649</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -13630,7 +13586,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>snowy_days_county_2002-2016</t>
+          <t>cold_days_p5_county_2002-2016</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -13661,12 +13617,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -13690,7 +13646,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>temp_30y_avg_county_1981-2010</t>
+          <t>cold_days_precip_county_2002-2016</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -13700,12 +13656,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>1981-2010</t>
+          <t>2002-2016</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1981-2010</t>
+          <t>2002-2016</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -13726,13 +13682,13 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13750,7 +13706,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>temp_30y_daily_avg_county_1981-2010</t>
+          <t>freezing_days_county_2002-2016</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -13760,12 +13716,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>1981-2010</t>
+          <t>2002-2016</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1981-2010</t>
+          <t>2002-2016</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
@@ -13781,18 +13737,18 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13810,7 +13766,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>temp_daily_avg_county_2002-2016</t>
+          <t>freezing_days_precip_county_2002-2016</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -13846,7 +13802,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -13861,6 +13817,474 @@
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>hot_days_p95_county_2002-2016</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>County (2010)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>stcofips10</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>hot_days_p99_county_2002-2016</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>NO_DICT</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>rainsnow_county_2002-2016</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>County (2010)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>stcofips10</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>rainy_days_county_2002-2016</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>County (2010)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>stcofips10</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>snowy_days_county_2002-2016</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>County (2010)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>stcofips10</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>temp_30y_avg_county_1981-2010</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>County (2010)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>1981-2010</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>1981-2010</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>stcofips10</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>temp_30y_daily_avg_county_1981-2010</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>County (2010)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>1981-2010</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>1981-2010</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>stcofips10</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>temp_daily_avg_county_2002-2016</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>County (2010)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2002-2016</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>stcofips10</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13873,7 +14297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14165,7 +14589,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>catalog_no_o_files</t>
+          <t>no_o_unit_in_folder</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -14173,28 +14597,36 @@
           <t>120088</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>crosswalks</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ZCTA merge CODE deposit, not a dataset - folder unclear (crosswalks? ZIPtoZCTA?)</t>
+          <t xml:space="preserve">chosen: </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>catalog_no_o_files</t>
+          <t>matched_unit_no_dict</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>141121</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>120088</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>crosswalks</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NO O: FILES - published to NaNDA as an external dataset (no local curation files)</t>
+          <t xml:space="preserve"> has no parseable dict on disk</t>
         </is>
       </c>
     </row>
@@ -14206,71 +14638,71 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>190141</t>
+          <t>141121</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NO O: FILES - special release built on Dropbox from merged NaNDA data (one-off)</t>
+          <t>NO O: FILES - published to NaNDA as an external dataset (no local curation files)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>multi_subfolder</t>
+          <t>catalog_no_o_files</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>230941</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PRISM</t>
-        </is>
-      </c>
+          <t>190141</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>chosen: ppt; tmax</t>
+          <t>NO O: FILES - special release built on Dropbox from merged NaNDA data (one-off)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>o_topic_no_catalog</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>multi_subfolder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>230941</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NHPD</t>
+          <t>PRISM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1 O: unit(s); no catalog deposit maps here</t>
+          <t>chosen: ppt; tmax</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>o_unit_unselected</t>
+          <t>o_topic_no_catalog</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PRISM</t>
+          <t>NHPD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>daily () not matched to a deposit</t>
+          <t>1 O: unit(s); no catalog deposit maps here</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14720,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>tmin (2010-2019) not matched to a deposit</t>
+          <t>daily () not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14301,12 +14733,12 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>arts_entertainment_recreation</t>
+          <t>PRISM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>artsentleisure_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>tmin (2010-2019) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14324,7 +14756,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>artsentrec_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>artsentleisure_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14774,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>artsentrec_tract_2006-2015 (2006-2015) not matched to a deposit</t>
+          <t>artsentrec_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14792,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>artsentrec_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>artsentrec_tract_2006-2015 (2006-2015) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14373,12 +14805,12 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>broadband</t>
+          <t>arts_entertainment_recreation</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>broadband_fcc_tract_2014-2018 (2014-2018) not matched to a deposit</t>
+          <t>artsentrec_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14396,7 +14828,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>broadband_fcc_zcta_2014-2018 (2014-2018) not matched to a deposit</t>
+          <t>broadband_fcc_tract_2014-2018 (2014-2018) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14409,12 +14841,12 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dollar_stores</t>
+          <t>broadband</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>dollar_stores_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>broadband_fcc_zcta_2014-2018 (2014-2018) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14864,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>dollar_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>dollar_stores_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14450,7 +14882,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>dollar_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>dollar_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14463,12 +14895,12 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>eating_drinking</t>
+          <t>dollar_stores</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>eatdrink_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>dollar_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14486,7 +14918,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>eatdrink_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>eatdrink_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14504,7 +14936,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>eatdrink_tract_2006-2015 (2006-2015) not matched to a deposit</t>
+          <t>eatdrink_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14522,7 +14954,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>eatdrink_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>eatdrink_tract_2006-2015 (2006-2015) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14535,12 +14967,12 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>education_training</t>
+          <t>eating_drinking</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>schools_nets_tract_2006-2015 (2006-2015) not matched to a deposit</t>
+          <t>eatdrink_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14553,12 +14985,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>grocery_stores</t>
+          <t>education_training</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>grocery_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>schools_nets_tract_2006-2015 (2006-2015) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14576,7 +15008,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>grocery_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>grocery_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14594,7 +15026,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>grocery_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>grocery_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14607,12 +15039,12 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>health_care_nets</t>
+          <t>grocery_stores</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>health_care_nets_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>grocery_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14630,7 +15062,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>health_care_nets_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>health_care_nets_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14648,7 +15080,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>health_care_nets_tract_2006-2015 (2006-2015) not matched to a deposit</t>
+          <t>health_care_nets_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14666,7 +15098,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>health_care_nets_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>health_care_nets_tract_2006-2015 (2006-2015) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14679,12 +15111,12 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>land_cover</t>
+          <t>health_care_nets</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>landcover_zcta_2001-2016 (2001-2016) not matched to a deposit</t>
+          <t>health_care_nets_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14697,12 +15129,12 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>law_enforcement</t>
+          <t>land_cover</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>justice_safety_tract_2006-2015 (2006-2015) not matched to a deposit</t>
+          <t>landcover_zcta_2001-2016 (2001-2016) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14720,7 +15152,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>lawenf_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>justice_safety_tract_2006-2015 (2006-2015) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14738,7 +15170,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>lawenf_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>lawenf_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14756,7 +15188,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>lawenf_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>lawenf_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14769,12 +15201,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>liquor_tobacco_convenience</t>
+          <t>law_enforcement</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>lqtbcon_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>lawenf_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14792,7 +15224,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lqtbcon_tractZCTA_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>lqtbcon_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14810,7 +15242,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>lqtbcon_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>lqtbcon_tractZCTA_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14823,12 +15255,12 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>parks</t>
+          <t>liquor_tobacco_convenience</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>parks_tract20_2022 (2022) not matched to a deposit</t>
+          <t>lqtbcon_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14846,7 +15278,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>parks_zcta20_2022 (2022) not matched to a deposit</t>
+          <t>parks_tract20_2022 (2022) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14859,12 +15291,12 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>personal_care_laundromats</t>
+          <t>parks</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>pclaund_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>parks_zcta20_2022 (2022) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14882,7 +15314,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>pclaund_tractZCTA_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>pclaund_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14900,7 +15332,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>pclaund_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>pclaund_tractZCTA_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14918,7 +15350,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>personal_services_tract_2006-2015 (2006-2015) not matched to a deposit</t>
+          <t>pclaund_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14931,12 +15363,12 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>pollution</t>
+          <t>personal_care_laundromats</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>polluting_sites_tract_2000-2018 (2000-2018) not matched to a deposit</t>
+          <t>personal_services_tract_2006-2015 (2006-2015) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14954,7 +15386,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>polluting_sites_zcta_2000-2018 (2000-2018) not matched to a deposit</t>
+          <t>polluting_sites_tract_2000-2018 (2000-2018) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14967,12 +15399,12 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>post_offices_banks</t>
+          <t>pollution</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>pobank_1990-2022 (1990-2022) not matched to a deposit</t>
+          <t>polluting_sites_zcta_2000-2018 (2000-2018) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -14990,7 +15422,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>pobank_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>pobank_1990-2022 (1990-2022) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15440,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>pobank_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>pobank_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15021,30 +15453,30 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>recreation</t>
+          <t>post_offices_banks</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>recreation_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>pobank_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>o_unit_unselected</t>
+          <t>o_topic_no_catalog</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>religious_civic_social_orgs</t>
+          <t>public_transit_quality</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>relcivsoc_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>6 O: unit(s); no catalog deposit maps here</t>
         </is>
       </c>
     </row>
@@ -15057,12 +15489,12 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>religious_civic_social_orgs</t>
+          <t>recreation</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>relcivsoc_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>recreation_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15080,7 +15512,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>relcivsoc_tract_2006-2015 (2006-2015) not matched to a deposit</t>
+          <t>relcivsoc_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15098,7 +15530,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>relcivsoc_zcta10_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>relcivsoc_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15116,7 +15548,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>relcivsoc_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>relcivsoc_tract_2006-2015 (2006-2015) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15129,12 +15561,12 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>retail_establishments</t>
+          <t>religious_civic_social_orgs</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>retail_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>relcivsoc_zcta10_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15147,12 +15579,12 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>retail_establishments</t>
+          <t>religious_civic_social_orgs</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>retail_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>relcivsoc_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15170,7 +15602,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>retail_tract_2006-2015 (2006-2015) not matched to a deposit</t>
+          <t>retail_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15188,7 +15620,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>retail_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>retail_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15201,12 +15633,12 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>schools</t>
+          <t>retail_establishments</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>neighborhood_school_gap_tract_supp_0910_1516 (2009-2010) not matched to a deposit</t>
+          <t>retail_tract_2006-2015 (2006-2015) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15219,12 +15651,12 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>schools</t>
+          <t>retail_establishments</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>neighborhood_school_gap_zcta_supp_0910_1516 (2009-2010) not matched to a deposit</t>
+          <t>retail_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15237,12 +15669,12 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ses_demographics</t>
+          <t>schools</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>sesdem_tract_1990 (1990) not matched to a deposit</t>
+          <t>neighborhood_school_gap_tract_supp_0910_1516 (2009-2010) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15255,12 +15687,12 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ses_demographics</t>
+          <t>schools</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>sesdem_tract_1990-2010 (1990-2010) not matched to a deposit</t>
+          <t>neighborhood_school_gap_zcta_supp_0910_1516 (2009-2010) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15278,7 +15710,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>sesdem_tract_2000-2010 (2000-2010) not matched to a deposit</t>
+          <t>sesdem_2019-2023 (2019-2023) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15296,7 +15728,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>sesdem_tract_2008-2017 (2008-2017) not matched to a deposit</t>
+          <t>sesdem_2020-2024 (2020-2024) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15746,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>sesdem_tract_2016-2020 (2016-2020) not matched to a deposit</t>
+          <t>sesdem_tract_1990 (1990) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15764,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>sesdem_zcta_2008-2017 (2008-2017) not matched to a deposit</t>
+          <t>sesdem_tract_1990-2010 (1990-2010) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15350,7 +15782,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>sesdem_zcta_2016-2020 (2016-2020) not matched to a deposit</t>
+          <t>sesdem_tract_2000-2010 (2000-2010) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15368,7 +15800,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>totpop_zcta_2000-2010 (2000-2010) not matched to a deposit</t>
+          <t>sesdem_tract_2008-2017 (2008-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15381,12 +15813,12 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>social_services</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>social_services_1990-2021 (1990-2021) not matched to a deposit</t>
+          <t>sesdem_tract_2016-2020 (2016-2020) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15399,12 +15831,12 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>social_services</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>social_services_tract_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>sesdem_zcta_2008-2017 (2008-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15417,12 +15849,12 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>social_services</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>social_services_tract_2006-2015 (2006-2015) not matched to a deposit</t>
+          <t>sesdem_zcta_2016-2020 (2016-2020) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15435,12 +15867,12 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>social_services</t>
+          <t>ses_demographics</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>social_services_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
+          <t>totpop_zcta_2000-2010 (2000-2010) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15453,12 +15885,12 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>social_services</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>street_type_tract_2020 (2020) not matched to a deposit</t>
+          <t>social_services_1990-2021 (1990-2021) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15471,12 +15903,12 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>social_services</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>street_type_zcta_2020 (2020) not matched to a deposit</t>
+          <t>social_services_tract_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15489,12 +15921,12 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>traffic</t>
+          <t>social_services</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>traffic_volume_noninterpolated_zcta_1963-2019 (1963-2019) not matched to a deposit</t>
+          <t>social_services_tract_2006-2015 (2006-2015) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15507,12 +15939,12 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>urbanicity</t>
+          <t>social_services</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>urbanicity_ruca_zip_2010 (2010) not matched to a deposit</t>
+          <t>social_services_zcta_2003-2017 (2003-2017) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15525,12 +15957,12 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>voting</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>voting_county_2004-2018 (2004-2018) not matched to a deposit</t>
+          <t>street_type_tract_2020 (2020) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15543,12 +15975,12 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>voting</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>voting_county_2018-2022 (2018-2022) not matched to a deposit</t>
+          <t>street_type_zcta_2020 (2020) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15561,12 +15993,12 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>traffic</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>hot_days_p99_county_2002-2016 (2002-2016) not matched to a deposit</t>
+          <t>traffic_volume_noninterpolated_zcta_1963-2019 (1963-2019) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15579,12 +16011,12 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>urbanicity</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>temp_30y_avg_county_1981-2010 (1981-2010) not matched to a deposit</t>
+          <t>urbanicity_ruca_zip_2010 (2010) not matched to a deposit</t>
         </is>
       </c>
     </row>
@@ -15597,10 +16029,82 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
+          <t>voting</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>voting_county_2004-2018 (2004-2018) not matched to a deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>o_unit_unselected</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>voting</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>voting_county_2018-2022 (2018-2022) not matched to a deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>o_unit_unselected</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
           <t>weather</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>hot_days_p99_county_2002-2016 (2002-2016) not matched to a deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>o_unit_unselected</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>temp_30y_avg_county_1981-2010 (1981-2010) not matched to a deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>o_unit_unselected</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
         <is>
           <t>temp_30y_daily_avg_county_1981-2010 (1981-2010) not matched to a deposit</t>
         </is>
@@ -16343,7 +16847,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>110663</t>
+          <t>120088</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -16353,11 +16857,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>tract_fips</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
@@ -16368,28 +16868,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>120088</t>
+          <t>127681</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>tract_fips10; year</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>tract_fips10 year</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>not in v03 oracle</t>
+          <t>oracle subfolder=edtrain_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>127681</t>
+          <t>127682</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -16409,12 +16925,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>tract_fips10; year</t>
+          <t>zcta19; year</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>tract_fips10 year</t>
+          <t>zcta19 year</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -16426,7 +16942,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>127682</t>
+          <t>141121</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -16436,84 +16952,80 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>DIFF mine= oracle=historic_redlining</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>match</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>match</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>zcta19; year</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>zcta19 year</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>oracle subfolder=edtrain_zcta_2003-2017</t>
+          <t>oracle subfolder=</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>141121</t>
+          <t>190141</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DIFF mine= oracle=historic_redlining</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>match</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>oracle subfolder=</t>
+          <t>not in v03 oracle</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>190141</t>
+          <t>200038</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>oracle_unfilled</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>not in v03 oracle</t>
+          <t>oracle subfolder=</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>200038</t>
+          <t>207966</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -16533,20 +17045,20 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>oracle subfolder=</t>
+          <t>oracle subfolder=relcivsoc_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>207966</t>
+          <t>208207</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -16572,14 +17084,14 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>oracle subfolder=relcivsoc_zcta_2003-2017</t>
+          <t>oracle subfolder=social_services_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>208207</t>
+          <t>208366</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -16599,20 +17111,20 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
+          <t>tract_fips10; year; tract_fips20; zcta20; zcta10</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>oracle subfolder=social_services_zcta_2003-2017</t>
+          <t>oracle subfolder=pobank_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>208366</t>
+          <t>208682</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -16632,20 +17144,20 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; zcta20; zcta10</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>oracle subfolder=pobank_zcta_2003-2017</t>
+          <t>oracle subfolder=retail_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>208682</t>
+          <t>208684</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -16671,14 +17183,14 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>oracle subfolder=retail_zcta_2003-2017</t>
+          <t>oracle subfolder=lawenf_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>208684</t>
+          <t>208751</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -16704,14 +17216,14 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>oracle subfolder=lawenf_zcta_2003-2017</t>
+          <t>oracle subfolder=eatdrink_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>208751</t>
+          <t>208906</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -16737,14 +17249,14 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>oracle subfolder=eatdrink_zcta_2003-2017</t>
+          <t>oracle subfolder=personal_services_tract_2006-2015</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>208906</t>
+          <t>208907</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -16770,14 +17282,14 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>oracle subfolder=personal_services_tract_2006-2015</t>
+          <t>oracle subfolder=lqtbcon_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>208907</t>
+          <t>209050</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -16803,14 +17315,14 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>oracle subfolder=lqtbcon_zcta_2003-2017</t>
+          <t>oracle subfolder=health_care_nets_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>209050</t>
+          <t>209163</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -16836,14 +17348,14 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>oracle subfolder=health_care_nets_zcta_2003-2017</t>
+          <t>oracle subfolder=artsentrec_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>209163</t>
+          <t>209164</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16869,14 +17381,14 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>oracle subfolder=artsentrec_zcta_2003-2017</t>
+          <t>oracle subfolder=recreation_1990-2021</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>209164</t>
+          <t>209313</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16902,14 +17414,14 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>oracle subfolder=recreation_1990-2021</t>
+          <t>oracle subfolder=grocery_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>209313</t>
+          <t>209324</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -16935,14 +17447,14 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>oracle subfolder=grocery_zcta_2003-2017</t>
+          <t>oracle subfolder=dollar_zcta_2003-2017</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>209324</t>
+          <t>210581</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -16962,20 +17474,20 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
+          <t>blkgrp_fips10; blkgrp_fips20</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>oracle subfolder=dollar_zcta_2003-2017</t>
+          <t>oracle subfolder=datasets</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>210581</t>
+          <t>220701</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -16990,25 +17502,29 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>oracle_unfilled</t>
+          <t>oracle_stale</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>blkgrp_fips10; blkgrp_fips20</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>zcta19 year</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>oracle subfolder=datasets</t>
+          <t>oracle subfolder=landcover_zcta_2001-2016</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>220701</t>
+          <t>222263</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -17023,7 +17539,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>oracle_stale</t>
+          <t>oracle_unfilled</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -17031,21 +17547,17 @@
           <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>zcta19 year</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>oracle subfolder=landcover_zcta_2001-2016</t>
+          <t>oracle subfolder=datasets</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>222263</t>
+          <t>222901</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -17065,20 +17577,20 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; zcta10; zcta20</t>
+          <t>tract_fips10; tract_fips20; zcta10; zcta20</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>oracle subfolder=datasets</t>
+          <t>oracle subfolder=</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>222901</t>
+          <t>230941</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -17098,20 +17610,20 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>tract_fips10; tract_fips20; zcta10; zcta20</t>
+          <t>year; tract_fips10; tract_fips20</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>oracle subfolder=</t>
+          <t>oracle subfolder=PRISM_v01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>230941</t>
+          <t>237305</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -17131,20 +17643,20 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>year; tract_fips10; tract_fips20</t>
+          <t>tract_fips10</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>oracle subfolder=PRISM_v01</t>
+          <t>oracle subfolder=datasets</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>237305</t>
+          <t>301419</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -17164,7 +17676,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>tract_fips10</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
@@ -17177,98 +17689,90 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>301419</t>
+          <t>302178</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>match</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>oracle_unfilled</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
+          <t>tract_fips20; tract_fips22; zcta_fips20</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>oracle subfolder=datasets</t>
+          <t>not in v03 oracle</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>302178</t>
+          <t>302343</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>oracle_unfilled</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>tract_fips20; tract_fips22; zcta_fips20</t>
+          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>not in v03 oracle</t>
+          <t>oracle subfolder=training_vocation_1990-2022</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>302343</t>
+          <t>302937</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>match</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>oracle_unfilled</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>tract_fips10; year; tract_fips20; tract_fips22; zcta10; zcta20</t>
+          <t>tract_fips20; tract_fips22; zcta20</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>oracle subfolder=training_vocation_1990-2022</t>
+          <t>not in v03 oracle</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>302937</t>
+          <t>305511</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -17293,7 +17797,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>305511</t>
+          <t>110663</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -17305,7 +17809,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>tract_fips20; tract_fips22; zcta20</t>
+          <t>tract_fips</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
